--- a/运气工程/运气工程-01-RTP-HitRate-波动率协同.xlsx
+++ b/运气工程/运气工程-01-RTP-HitRate-波动率协同.xlsx
@@ -1142,6 +1142,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F67" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1534,6 +1537,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J42" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2076,6 +2082,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M40" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2756,6 +2765,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J59" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3026,5 +3038,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H43" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/运气工程/运气工程-01-RTP-HitRate-波动率协同.xlsx
+++ b/运气工程/运气工程-01-RTP-HitRate-波动率协同.xlsx
@@ -393,6 +393,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
+  </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -499,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -556,6 +559,15 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1317,7 +1329,7 @@
       <c r="A10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="21">
         <f>B5*B6/B4</f>
       </c>
       <c r="C10" s="2" t="s">
@@ -1334,7 +1346,7 @@
       <c r="A11" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="22">
         <f>1-B10</f>
       </c>
       <c r="C11" s="2" t="s">
@@ -1419,7 +1431,7 @@
       <c r="A16" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="22">
         <f>B10-B7</f>
       </c>
       <c r="C16" s="2" t="s">
@@ -1493,7 +1505,7 @@
       <c r="C20" s="15">
         <f>B6</f>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="22">
         <f>B20*C20/B4</f>
       </c>
       <c r="E20" s="17" t="s">
@@ -1510,7 +1522,7 @@
       <c r="C21" s="16">
         <f>$B$7/B21</f>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="22">
         <f>B21*C21/B4</f>
       </c>
       <c r="E21" s="2" t="s">
@@ -1527,7 +1539,7 @@
       <c r="C22" s="16">
         <f>$B$7/B22</f>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="22">
         <f>B22*C22/B4</f>
       </c>
       <c r="E22" s="2" t="s">
@@ -1751,7 +1763,7 @@
       <c r="C8" s="15">
         <f>$B$4/B8</f>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="21">
         <f>B8*C8</f>
       </c>
       <c r="E8" s="15">
@@ -1777,7 +1789,7 @@
       <c r="C9" s="15">
         <f>$B$4/B9</f>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="21">
         <f>B9*C9</f>
       </c>
       <c r="E9" s="15">
@@ -1803,7 +1815,7 @@
       <c r="C10" s="15">
         <f>$B$4/B10</f>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="21">
         <f>B10*C10</f>
       </c>
       <c r="E10" s="15">
@@ -1829,7 +1841,7 @@
       <c r="C11" s="15">
         <f>$B$4/B11</f>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="21">
         <f>B11*C11</f>
       </c>
       <c r="E11" s="15">
@@ -1927,19 +1939,19 @@
       <c r="A15" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="22">
         <f>B8</f>
       </c>
       <c r="C15" s="15">
         <f>1/B15</f>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="22">
         <f>(1-B15)^10</f>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="22">
         <f>(1-B15)^20</f>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="22">
         <f>(1-B15)^50</f>
       </c>
       <c r="G15" s="9" t="s">
@@ -1953,19 +1965,19 @@
       <c r="A16" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="22">
         <f>B9</f>
       </c>
       <c r="C16" s="15">
         <f>1/B16</f>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="22">
         <f>(1-B16)^10</f>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="22">
         <f>(1-B16)^20</f>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="22">
         <f>(1-B16)^50</f>
       </c>
       <c r="G16" s="9" t="s">
@@ -1979,19 +1991,19 @@
       <c r="A17" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="22">
         <f>B10</f>
       </c>
       <c r="C17" s="15">
         <f>1/B17</f>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="22">
         <f>(1-B17)^10</f>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="22">
         <f>(1-B17)^20</f>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="22">
         <f>(1-B17)^50</f>
       </c>
       <c r="G17" s="9" t="s">
@@ -2005,19 +2017,19 @@
       <c r="A18" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="22">
         <f>B11</f>
       </c>
       <c r="C18" s="15">
         <f>1/B18</f>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="22">
         <f>(1-B18)^10</f>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="22">
         <f>(1-B18)^20</f>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="22">
         <f>(1-B18)^50</f>
       </c>
       <c r="G18" s="9" t="s">
@@ -2222,10 +2234,10 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="22">
         <f>(1-$B$4)^A8</f>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="22">
         <f>1-B8</f>
       </c>
       <c r="D8" s="9" t="s">
@@ -2239,10 +2251,10 @@
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="22">
         <f>(1-$B$4)^A9</f>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="22">
         <f>1-B9</f>
       </c>
       <c r="D9" s="9" t="s">
@@ -2256,10 +2268,10 @@
       <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="22">
         <f>(1-$B$4)^A10</f>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="22">
         <f>1-B10</f>
       </c>
       <c r="D10" s="9" t="s">
@@ -2273,10 +2285,10 @@
       <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="22">
         <f>(1-$B$4)^A11</f>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="22">
         <f>1-B11</f>
       </c>
       <c r="D11" s="9" t="s">
@@ -2290,10 +2302,10 @@
       <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="22">
         <f>(1-$B$4)^A12</f>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="22">
         <f>1-B12</f>
       </c>
       <c r="D12" s="9" t="s">
@@ -2307,10 +2319,10 @@
       <c r="A13">
         <v>6</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="22">
         <f>(1-$B$4)^A13</f>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="22">
         <f>1-B13</f>
       </c>
       <c r="D13" s="9" t="s">
@@ -2324,10 +2336,10 @@
       <c r="A14">
         <v>7</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="22">
         <f>(1-$B$4)^A14</f>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="22">
         <f>1-B14</f>
       </c>
       <c r="D14" s="9" t="s">
@@ -2341,10 +2353,10 @@
       <c r="A15">
         <v>8</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="22">
         <f>(1-$B$4)^A15</f>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="22">
         <f>1-B15</f>
       </c>
       <c r="D15" s="9" t="s">
@@ -2358,10 +2370,10 @@
       <c r="A16">
         <v>9</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="22">
         <f>(1-$B$4)^A16</f>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="22">
         <f>1-B16</f>
       </c>
       <c r="D16" s="9" t="s">
@@ -2375,10 +2387,10 @@
       <c r="A17">
         <v>10</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="22">
         <f>(1-$B$4)^A17</f>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="22">
         <f>1-B17</f>
       </c>
       <c r="D17" s="9" t="s">
@@ -2392,10 +2404,10 @@
       <c r="A18">
         <v>11</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="22">
         <f>(1-$B$4)^A18</f>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="22">
         <f>1-B18</f>
       </c>
       <c r="D18" s="9" t="s">
@@ -2409,10 +2421,10 @@
       <c r="A19">
         <v>12</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="22">
         <f>(1-$B$4)^A19</f>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="22">
         <f>1-B19</f>
       </c>
       <c r="D19" s="9" t="s">
@@ -2426,10 +2438,10 @@
       <c r="A20">
         <v>13</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="22">
         <f>(1-$B$4)^A20</f>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="22">
         <f>1-B20</f>
       </c>
       <c r="D20" s="9" t="s">
@@ -2443,10 +2455,10 @@
       <c r="A21">
         <v>14</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="22">
         <f>(1-$B$4)^A21</f>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="22">
         <f>1-B21</f>
       </c>
       <c r="D21" s="9" t="s">
@@ -2460,10 +2472,10 @@
       <c r="A22">
         <v>15</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="22">
         <f>(1-$B$4)^A22</f>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="22">
         <f>1-B22</f>
       </c>
       <c r="D22" s="9" t="s">
@@ -2477,10 +2489,10 @@
       <c r="A23">
         <v>16</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="22">
         <f>(1-$B$4)^A23</f>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="22">
         <f>1-B23</f>
       </c>
       <c r="D23" s="9" t="s">
@@ -2494,10 +2506,10 @@
       <c r="A24">
         <v>17</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="22">
         <f>(1-$B$4)^A24</f>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="22">
         <f>1-B24</f>
       </c>
       <c r="D24" s="9" t="s">
@@ -2511,10 +2523,10 @@
       <c r="A25">
         <v>18</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="22">
         <f>(1-$B$4)^A25</f>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="22">
         <f>1-B25</f>
       </c>
       <c r="D25" s="9" t="s">
@@ -2528,10 +2540,10 @@
       <c r="A26">
         <v>19</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="22">
         <f>(1-$B$4)^A26</f>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="22">
         <f>1-B26</f>
       </c>
       <c r="D26" s="9" t="s">
@@ -2545,10 +2557,10 @@
       <c r="A27">
         <v>20</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="22">
         <f>(1-$B$4)^A27</f>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="22">
         <f>1-B27</f>
       </c>
       <c r="D27" s="9" t="s">
@@ -2613,7 +2625,7 @@
       <c r="A31" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="22">
         <f>(1-$B$4)^10</f>
       </c>
       <c r="C31" s="14" t="s">
@@ -2684,13 +2696,13 @@
       <c r="B35" s="15">
         <f>1/A35</f>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="22">
         <f>(1-A35)^20</f>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="22">
         <f>(1-A35)^50</f>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="22">
         <f>(1-A35)^100</f>
       </c>
     </row>
@@ -2701,13 +2713,13 @@
       <c r="B36" s="15">
         <f>1/A36</f>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="22">
         <f>(1-A36)^20</f>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="22">
         <f>(1-A36)^50</f>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="22">
         <f>(1-A36)^100</f>
       </c>
     </row>
@@ -2718,13 +2730,13 @@
       <c r="B37" s="15">
         <f>1/A37</f>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="22">
         <f>(1-A37)^20</f>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="22">
         <f>(1-A37)^50</f>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="22">
         <f>(1-A37)^100</f>
       </c>
     </row>
@@ -2735,13 +2747,13 @@
       <c r="B38" s="15">
         <f>1/A38</f>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="22">
         <f>(1-A38)^20</f>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="22">
         <f>(1-A38)^50</f>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="22">
         <f>(1-A38)^100</f>
       </c>
     </row>
@@ -2752,13 +2764,13 @@
       <c r="B39" s="15">
         <f>1/A39</f>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="22">
         <f>(1-A39)^20</f>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="22">
         <f>(1-A39)^50</f>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="22">
         <f>(1-A39)^100</f>
       </c>
     </row>
@@ -2896,7 +2908,7 @@
       <c r="A11" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="21">
         <f>B9/B10</f>
       </c>
       <c r="C11" s="2" t="s">
@@ -2951,7 +2963,7 @@
       <c r="A16" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="21">
         <f>B14*B15</f>
       </c>
       <c r="C16" s="2" t="s">
@@ -2995,7 +3007,7 @@
       <c r="A20" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="22">
         <f>B19/B15-1</f>
       </c>
       <c r="C20" s="2" t="s">
@@ -3006,7 +3018,7 @@
       <c r="A21" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="22">
         <f>B18*B19</f>
       </c>
       <c r="C21" s="2" t="s">
